--- a/DateBase/orders/Nha Thu_2026-6-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-4.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01301021055510180</v>
+        <v>01301021055510181</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,12 +521,92 @@
         <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>169_欢乐颂_Silantoi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01301021055510181</v>
+        <v>01301021055510181551010101576650</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -603,10 +603,97 @@
       <c r="C21" t="str">
         <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>516_火焰兰_Crocosmia_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>6</v>
+      </c>
+      <c r="C28" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -661,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01301021055510181551010101576650</v>
+        <v>01301021055510181551010101576651011101510103515103</v>
       </c>
     </row>
   </sheetData>
